--- a/sample_templates/浆粕原料流水.xlsx
+++ b/sample_templates/浆粕原料流水.xlsx
@@ -417,56 +417,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>创建时间</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>单据号</t>
+          <t>物料编号</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>物料编码</t>
+          <t>物料名称</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>物料名称</t>
+          <t>分类名称</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数量(kg)</t>
+          <t>物料规格</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>单价</t>
+          <t>仓库名称</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>批次号</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>操作数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>单位名称</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>业务类型</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>车间</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -480,29 +504,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OUT-2026073100015</t>
+          <t>示例-R82.101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>示例-R82.205</t>
+          <t>示例对位芳纶回收料-乱丝</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>示例对位芳纶回收料-进口开松料</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>原料仓</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>5000</v>
       </c>
-      <c r="F2" t="n">
-        <v>52.1981</v>
-      </c>
-      <c r="G2" t="n">
-        <v>260990.68</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>千克</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>领料出库</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>浆粕车间</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>浆粕车间7月领用</t>
         </is>
@@ -516,29 +556,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OUT-2026073100021</t>
+          <t>示例-R84.101</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>示例-R84.101</t>
+          <t>示例国产聚丙烯腈丝束</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>示例国产聚丙烯腈丝束</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>原料仓</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>20000</v>
       </c>
-      <c r="F3" t="n">
-        <v>19.5581</v>
-      </c>
-      <c r="G3" t="n">
-        <v>391162.88</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>千克</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>领料出库</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>浆粕车间</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>浆粕车间7月领用</t>
         </is>
@@ -547,7 +603,7 @@
     <row r="4">
       <c r="D4" t="inlineStr">
         <is>
-          <t>（示例行自动跳过；物料名称须含「芳纶」或「腈」）</t>
+          <t>（示例行自动跳过；材料成本只统计业务类型为“领料出库”的行；金额无需填写，系统按历史单价 出库价优先、入库价兜底 自动计算）</t>
         </is>
       </c>
     </row>
